--- a/del-agent/skills/del-excel-filler/template.xlsx
+++ b/del-agent/skills/del-excel-filler/template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\实习资料\面试-产出\devCR-new\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HuaweiMoveData\Users\lyh\Desktop\AI-Aesthetic-Judge\AI-Aesthetic-Judge\del-agent\skills\del-excel-filler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9317786E-D125-4D2E-AB0F-6F11E8A15FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{950F1D18-5EB0-4045-99F5-B15BD1F6170B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11400" yWindow="3336" windowWidth="11640" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="服务岗位面试评价表" sheetId="7" r:id="rId1"/>
@@ -87,9 +87,6 @@
   </si>
   <si>
     <t>专业</t>
-  </si>
-  <si>
-    <t>高考数学成绩</t>
   </si>
   <si>
     <t>面试方式</t>
@@ -1897,12 +1894,16 @@
       <t>转正后&amp;晋级：年度目标达成情况，参考通道图</t>
     </r>
   </si>
+  <si>
+    <t>高考数学成绩</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2038,6 +2039,13 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="19">
@@ -2455,7 +2463,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="187">
+  <cellXfs count="188">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2679,14 +2687,269 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2700,259 +2963,31 @@
     <xf numFmtId="0" fontId="12" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2961,30 +2996,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2994,8 +3005,17 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3003,17 +3023,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6021,48 +6032,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="24" customHeight="1">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="131" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="75"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="131"/>
+      <c r="M1" s="131"/>
+      <c r="N1" s="131"/>
+      <c r="O1" s="131"/>
     </row>
     <row r="2" spans="1:15" ht="24" customHeight="1">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="129" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="77" t="s">
+      <c r="B2" s="129"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="130" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77" t="s">
+      <c r="H2" s="130"/>
+      <c r="I2" s="130"/>
+      <c r="J2" s="130" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="75" t="s">
+      <c r="K2" s="130"/>
+      <c r="L2" s="130"/>
+      <c r="M2" s="131" t="s">
         <v>4</v>
       </c>
-      <c r="N2" s="75"/>
-      <c r="O2" s="75"/>
+      <c r="N2" s="131"/>
+      <c r="O2" s="131"/>
     </row>
     <row r="3" spans="1:15" ht="28.95" customHeight="1">
       <c r="A3" s="40" t="s">
@@ -6077,21 +6088,21 @@
         <v>7</v>
       </c>
       <c r="F3" s="45"/>
-      <c r="G3" s="78" t="s">
+      <c r="G3" s="163" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="78"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="80" t="s">
+      <c r="H3" s="163"/>
+      <c r="I3" s="164"/>
+      <c r="J3" s="165" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="80"/>
-      <c r="L3" s="81"/>
-      <c r="M3" s="82" t="s">
+      <c r="K3" s="165"/>
+      <c r="L3" s="166"/>
+      <c r="M3" s="145" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="83"/>
-      <c r="O3" s="84"/>
+      <c r="N3" s="146"/>
+      <c r="O3" s="147"/>
     </row>
     <row r="4" spans="1:15" ht="22.95" customHeight="1">
       <c r="A4" s="46" t="s">
@@ -6108,15 +6119,15 @@
       <c r="F4" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="85"/>
-      <c r="H4" s="86"/>
-      <c r="I4" s="87"/>
-      <c r="J4" s="88"/>
-      <c r="K4" s="89"/>
-      <c r="L4" s="90"/>
-      <c r="M4" s="82"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="84"/>
+      <c r="G4" s="157"/>
+      <c r="H4" s="158"/>
+      <c r="I4" s="159"/>
+      <c r="J4" s="160"/>
+      <c r="K4" s="161"/>
+      <c r="L4" s="162"/>
+      <c r="M4" s="145"/>
+      <c r="N4" s="146"/>
+      <c r="O4" s="147"/>
     </row>
     <row r="5" spans="1:15" ht="19.95" customHeight="1">
       <c r="A5" s="46" t="s">
@@ -6127,782 +6138,902 @@
         <v>16</v>
       </c>
       <c r="D5" s="43"/>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="187" t="s">
+        <v>138</v>
+      </c>
+      <c r="F5" s="43"/>
+      <c r="G5" s="148" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="45"/>
-      <c r="G5" s="91" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="91"/>
-      <c r="I5" s="91"/>
-      <c r="J5" s="92" t="s">
-        <v>18</v>
-      </c>
-      <c r="K5" s="92"/>
-      <c r="L5" s="92"/>
-      <c r="M5" s="82" t="s">
-        <v>18</v>
-      </c>
-      <c r="N5" s="83"/>
-      <c r="O5" s="84"/>
+      <c r="H5" s="148"/>
+      <c r="I5" s="148"/>
+      <c r="J5" s="149" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" s="149"/>
+      <c r="L5" s="149"/>
+      <c r="M5" s="145" t="s">
+        <v>17</v>
+      </c>
+      <c r="N5" s="146"/>
+      <c r="O5" s="147"/>
     </row>
     <row r="6" spans="1:15" ht="22.95" customHeight="1">
       <c r="A6" s="50" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="51"/>
       <c r="C6" s="52" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" s="52"/>
       <c r="E6" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="93"/>
-      <c r="H6" s="94"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="96"/>
-      <c r="K6" s="97"/>
-      <c r="L6" s="98"/>
-      <c r="M6" s="99"/>
-      <c r="N6" s="99"/>
-      <c r="O6" s="99"/>
+      <c r="G6" s="150"/>
+      <c r="H6" s="151"/>
+      <c r="I6" s="152"/>
+      <c r="J6" s="153"/>
+      <c r="K6" s="154"/>
+      <c r="L6" s="155"/>
+      <c r="M6" s="156"/>
+      <c r="N6" s="156"/>
+      <c r="O6" s="156"/>
     </row>
     <row r="7" spans="1:15" ht="22.95" customHeight="1">
       <c r="A7" s="50" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7" s="51"/>
       <c r="C7" s="52" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="45"/>
+      <c r="G7" s="157"/>
+      <c r="H7" s="158"/>
+      <c r="I7" s="159"/>
+      <c r="J7" s="160"/>
+      <c r="K7" s="161"/>
+      <c r="L7" s="162"/>
+      <c r="M7" s="145"/>
+      <c r="N7" s="146"/>
+      <c r="O7" s="147"/>
+    </row>
+    <row r="8" spans="1:15" ht="24" customHeight="1">
+      <c r="A8" s="131" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="45"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="86"/>
-      <c r="I7" s="87"/>
-      <c r="J7" s="88"/>
-      <c r="K7" s="89"/>
-      <c r="L7" s="90"/>
-      <c r="M7" s="82"/>
-      <c r="N7" s="83"/>
-      <c r="O7" s="84"/>
-    </row>
-    <row r="8" spans="1:15" ht="24" customHeight="1">
-      <c r="A8" s="75" t="s">
+      <c r="B8" s="131"/>
+      <c r="C8" s="131"/>
+      <c r="D8" s="131"/>
+      <c r="E8" s="131"/>
+      <c r="F8" s="131"/>
+      <c r="G8" s="131"/>
+      <c r="H8" s="131"/>
+      <c r="I8" s="131"/>
+      <c r="J8" s="131"/>
+      <c r="K8" s="131"/>
+      <c r="L8" s="131"/>
+      <c r="M8" s="131"/>
+      <c r="N8" s="131"/>
+      <c r="O8" s="131"/>
+    </row>
+    <row r="9" spans="1:15" ht="24" customHeight="1">
+      <c r="A9" s="129" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="75"/>
-      <c r="C8" s="75"/>
-      <c r="D8" s="75"/>
-      <c r="E8" s="75"/>
-      <c r="F8" s="75"/>
-      <c r="G8" s="75"/>
-      <c r="H8" s="75"/>
-      <c r="I8" s="75"/>
-      <c r="J8" s="75"/>
-      <c r="K8" s="75"/>
-      <c r="L8" s="75"/>
-      <c r="M8" s="75"/>
-      <c r="N8" s="75"/>
-      <c r="O8" s="75"/>
-    </row>
-    <row r="9" spans="1:15" ht="24" customHeight="1">
-      <c r="A9" s="76" t="s">
+      <c r="B9" s="129"/>
+      <c r="C9" s="129"/>
+      <c r="D9" s="129"/>
+      <c r="E9" s="129"/>
+      <c r="F9" s="129"/>
+      <c r="G9" s="130" t="s">
+        <v>2</v>
+      </c>
+      <c r="H9" s="130"/>
+      <c r="I9" s="130"/>
+      <c r="J9" s="130" t="s">
+        <v>3</v>
+      </c>
+      <c r="K9" s="130"/>
+      <c r="L9" s="130"/>
+      <c r="M9" s="131" t="s">
+        <v>4</v>
+      </c>
+      <c r="N9" s="131"/>
+      <c r="O9" s="131"/>
+    </row>
+    <row r="10" spans="1:15" ht="22.95" customHeight="1">
+      <c r="A10" s="136"/>
+      <c r="B10" s="137"/>
+      <c r="C10" s="137"/>
+      <c r="D10" s="137"/>
+      <c r="E10" s="137"/>
+      <c r="F10" s="138"/>
+      <c r="G10" s="139"/>
+      <c r="H10" s="140"/>
+      <c r="I10" s="141"/>
+      <c r="J10" s="142"/>
+      <c r="K10" s="143"/>
+      <c r="L10" s="144"/>
+      <c r="M10" s="145"/>
+      <c r="N10" s="146"/>
+      <c r="O10" s="147"/>
+    </row>
+    <row r="11" spans="1:15" ht="22.95" customHeight="1">
+      <c r="A11" s="136"/>
+      <c r="B11" s="137"/>
+      <c r="C11" s="137"/>
+      <c r="D11" s="137"/>
+      <c r="E11" s="137"/>
+      <c r="F11" s="138"/>
+      <c r="G11" s="139"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="141"/>
+      <c r="J11" s="142"/>
+      <c r="K11" s="143"/>
+      <c r="L11" s="144"/>
+      <c r="M11" s="145"/>
+      <c r="N11" s="146"/>
+      <c r="O11" s="147"/>
+    </row>
+    <row r="12" spans="1:15" ht="22.95" customHeight="1">
+      <c r="A12" s="136"/>
+      <c r="B12" s="137"/>
+      <c r="C12" s="137"/>
+      <c r="D12" s="137"/>
+      <c r="E12" s="137"/>
+      <c r="F12" s="138"/>
+      <c r="G12" s="139"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="141"/>
+      <c r="J12" s="142"/>
+      <c r="K12" s="143"/>
+      <c r="L12" s="144"/>
+      <c r="M12" s="145"/>
+      <c r="N12" s="146"/>
+      <c r="O12" s="147"/>
+    </row>
+    <row r="13" spans="1:15" ht="24" customHeight="1">
+      <c r="A13" s="131" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="76"/>
-      <c r="C9" s="76"/>
-      <c r="D9" s="76"/>
-      <c r="E9" s="76"/>
-      <c r="F9" s="76"/>
-      <c r="G9" s="77" t="s">
+      <c r="B13" s="131"/>
+      <c r="C13" s="131"/>
+      <c r="D13" s="131"/>
+      <c r="E13" s="131"/>
+      <c r="F13" s="131"/>
+      <c r="G13" s="131"/>
+      <c r="H13" s="131"/>
+      <c r="I13" s="131"/>
+      <c r="J13" s="131"/>
+      <c r="K13" s="131"/>
+      <c r="L13" s="131"/>
+      <c r="M13" s="131"/>
+      <c r="N13" s="131"/>
+      <c r="O13" s="131"/>
+    </row>
+    <row r="14" spans="1:15" ht="24" customHeight="1">
+      <c r="A14" s="129" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="129"/>
+      <c r="C14" s="129"/>
+      <c r="D14" s="129"/>
+      <c r="E14" s="129"/>
+      <c r="F14" s="129"/>
+      <c r="G14" s="130" t="s">
         <v>2</v>
       </c>
-      <c r="H9" s="77"/>
-      <c r="I9" s="77"/>
-      <c r="J9" s="77" t="s">
+      <c r="H14" s="130"/>
+      <c r="I14" s="130"/>
+      <c r="J14" s="130" t="s">
         <v>3</v>
       </c>
-      <c r="K9" s="77"/>
-      <c r="L9" s="77"/>
-      <c r="M9" s="75" t="s">
+      <c r="K14" s="130"/>
+      <c r="L14" s="130"/>
+      <c r="M14" s="131" t="s">
         <v>4</v>
       </c>
-      <c r="N9" s="75"/>
-      <c r="O9" s="75"/>
-    </row>
-    <row r="10" spans="1:15" ht="22.95" customHeight="1">
-      <c r="A10" s="100"/>
-      <c r="B10" s="101"/>
-      <c r="C10" s="101"/>
-      <c r="D10" s="101"/>
-      <c r="E10" s="101"/>
-      <c r="F10" s="102"/>
-      <c r="G10" s="103"/>
-      <c r="H10" s="104"/>
-      <c r="I10" s="105"/>
-      <c r="J10" s="106"/>
-      <c r="K10" s="107"/>
-      <c r="L10" s="108"/>
-      <c r="M10" s="82"/>
-      <c r="N10" s="83"/>
-      <c r="O10" s="84"/>
-    </row>
-    <row r="11" spans="1:15" ht="22.95" customHeight="1">
-      <c r="A11" s="100"/>
-      <c r="B11" s="101"/>
-      <c r="C11" s="101"/>
-      <c r="D11" s="101"/>
-      <c r="E11" s="101"/>
-      <c r="F11" s="102"/>
-      <c r="G11" s="103"/>
-      <c r="H11" s="104"/>
-      <c r="I11" s="105"/>
-      <c r="J11" s="106"/>
-      <c r="K11" s="107"/>
-      <c r="L11" s="108"/>
-      <c r="M11" s="82"/>
-      <c r="N11" s="83"/>
-      <c r="O11" s="84"/>
-    </row>
-    <row r="12" spans="1:15" ht="22.95" customHeight="1">
-      <c r="A12" s="100"/>
-      <c r="B12" s="101"/>
-      <c r="C12" s="101"/>
-      <c r="D12" s="101"/>
-      <c r="E12" s="101"/>
-      <c r="F12" s="102"/>
-      <c r="G12" s="103"/>
-      <c r="H12" s="104"/>
-      <c r="I12" s="105"/>
-      <c r="J12" s="106"/>
-      <c r="K12" s="107"/>
-      <c r="L12" s="108"/>
-      <c r="M12" s="82"/>
-      <c r="N12" s="83"/>
-      <c r="O12" s="84"/>
-    </row>
-    <row r="13" spans="1:15" ht="24" customHeight="1">
-      <c r="A13" s="75" t="s">
+      <c r="N14" s="131"/>
+      <c r="O14" s="131"/>
+    </row>
+    <row r="15" spans="1:15" ht="24" customHeight="1">
+      <c r="A15" s="131" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="75"/>
-      <c r="C13" s="75"/>
-      <c r="D13" s="75"/>
-      <c r="E13" s="75"/>
-      <c r="F13" s="75"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="75"/>
-      <c r="I13" s="75"/>
-      <c r="J13" s="75"/>
-      <c r="K13" s="75"/>
-      <c r="L13" s="75"/>
-      <c r="M13" s="75"/>
-      <c r="N13" s="75"/>
-      <c r="O13" s="75"/>
-    </row>
-    <row r="14" spans="1:15" ht="24" customHeight="1">
-      <c r="A14" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="B14" s="76"/>
-      <c r="C14" s="76"/>
-      <c r="D14" s="76"/>
-      <c r="E14" s="76"/>
-      <c r="F14" s="76"/>
-      <c r="G14" s="77" t="s">
-        <v>2</v>
-      </c>
-      <c r="H14" s="77"/>
-      <c r="I14" s="77"/>
-      <c r="J14" s="77" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="77"/>
-      <c r="L14" s="77"/>
-      <c r="M14" s="75" t="s">
-        <v>4</v>
-      </c>
-      <c r="N14" s="75"/>
-      <c r="O14" s="75"/>
-    </row>
-    <row r="15" spans="1:15" ht="24" customHeight="1">
-      <c r="A15" s="75" t="s">
+      <c r="B15" s="131"/>
+      <c r="C15" s="131"/>
+      <c r="D15" s="131" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="75"/>
-      <c r="C15" s="75"/>
-      <c r="D15" s="75" t="s">
+      <c r="E15" s="131" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="75" t="s">
+      <c r="F15" s="131"/>
+      <c r="G15" s="131" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="75"/>
-      <c r="G15" s="75" t="s">
-        <v>32</v>
-      </c>
-      <c r="H15" s="75" t="s">
+      <c r="H15" s="131" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="131"/>
+      <c r="J15" s="131" t="s">
         <v>31</v>
       </c>
-      <c r="I15" s="75"/>
-      <c r="J15" s="75" t="s">
-        <v>32</v>
-      </c>
-      <c r="K15" s="75" t="s">
+      <c r="K15" s="131" t="s">
+        <v>30</v>
+      </c>
+      <c r="L15" s="131"/>
+      <c r="M15" s="131" t="s">
         <v>31</v>
       </c>
-      <c r="L15" s="75"/>
-      <c r="M15" s="75" t="s">
-        <v>32</v>
-      </c>
-      <c r="N15" s="75" t="s">
-        <v>31</v>
-      </c>
-      <c r="O15" s="75"/>
+      <c r="N15" s="131" t="s">
+        <v>30</v>
+      </c>
+      <c r="O15" s="131"/>
     </row>
     <row r="16" spans="1:15" ht="24" customHeight="1">
       <c r="A16" s="54" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B16" s="55"/>
       <c r="C16" s="56"/>
       <c r="D16" s="57"/>
-      <c r="E16" s="109"/>
-      <c r="F16" s="109"/>
+      <c r="E16" s="132"/>
+      <c r="F16" s="132"/>
       <c r="G16" s="58"/>
-      <c r="H16" s="110"/>
-      <c r="I16" s="110"/>
+      <c r="H16" s="133"/>
+      <c r="I16" s="133"/>
       <c r="J16" s="59"/>
-      <c r="K16" s="111"/>
-      <c r="L16" s="111"/>
+      <c r="K16" s="134"/>
+      <c r="L16" s="134"/>
       <c r="M16" s="60"/>
-      <c r="N16" s="112"/>
-      <c r="O16" s="112"/>
+      <c r="N16" s="135"/>
+      <c r="O16" s="135"/>
     </row>
     <row r="17" spans="1:17" ht="28.95" customHeight="1">
-      <c r="A17" s="159" t="s">
+      <c r="A17" s="79" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="62" t="s">
         <v>34</v>
-      </c>
-      <c r="B17" s="62" t="s">
-        <v>35</v>
       </c>
       <c r="C17" s="63"/>
       <c r="D17" s="57"/>
-      <c r="E17" s="113"/>
-      <c r="F17" s="113"/>
+      <c r="E17" s="120"/>
+      <c r="F17" s="120"/>
       <c r="G17" s="58"/>
-      <c r="H17" s="114"/>
-      <c r="I17" s="114"/>
+      <c r="H17" s="121"/>
+      <c r="I17" s="121"/>
       <c r="J17" s="59"/>
-      <c r="K17" s="115"/>
-      <c r="L17" s="115"/>
+      <c r="K17" s="122"/>
+      <c r="L17" s="122"/>
       <c r="M17" s="60"/>
-      <c r="N17" s="116"/>
-      <c r="O17" s="116"/>
+      <c r="N17" s="119"/>
+      <c r="O17" s="119"/>
     </row>
     <row r="18" spans="1:17" ht="28.95" customHeight="1">
-      <c r="A18" s="160"/>
-      <c r="B18" s="162" t="s">
+      <c r="A18" s="80"/>
+      <c r="B18" s="82" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="64" t="s">
+      <c r="D18" s="57"/>
+      <c r="E18" s="106"/>
+      <c r="F18" s="107"/>
+      <c r="G18" s="58"/>
+      <c r="H18" s="123"/>
+      <c r="I18" s="124"/>
+      <c r="J18" s="59"/>
+      <c r="K18" s="125"/>
+      <c r="L18" s="126"/>
+      <c r="M18" s="60"/>
+      <c r="N18" s="127"/>
+      <c r="O18" s="128"/>
+    </row>
+    <row r="19" spans="1:17" ht="28.95" customHeight="1">
+      <c r="A19" s="80"/>
+      <c r="B19" s="82"/>
+      <c r="C19" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="57"/>
-      <c r="E18" s="117"/>
-      <c r="F18" s="118"/>
-      <c r="G18" s="58"/>
-      <c r="H18" s="119"/>
-      <c r="I18" s="120"/>
-      <c r="J18" s="59"/>
-      <c r="K18" s="121"/>
-      <c r="L18" s="122"/>
-      <c r="M18" s="60"/>
-      <c r="N18" s="123"/>
-      <c r="O18" s="124"/>
-    </row>
-    <row r="19" spans="1:17" ht="28.95" customHeight="1">
-      <c r="A19" s="160"/>
-      <c r="B19" s="162"/>
-      <c r="C19" s="64" t="s">
+      <c r="D19" s="57"/>
+      <c r="E19" s="106"/>
+      <c r="F19" s="107"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="123"/>
+      <c r="I19" s="124"/>
+      <c r="J19" s="59"/>
+      <c r="K19" s="125"/>
+      <c r="L19" s="126"/>
+      <c r="M19" s="60"/>
+      <c r="N19" s="127"/>
+      <c r="O19" s="128"/>
+    </row>
+    <row r="20" spans="1:17" ht="30" customHeight="1">
+      <c r="A20" s="80"/>
+      <c r="B20" s="83"/>
+      <c r="C20" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="D19" s="57"/>
-      <c r="E19" s="117"/>
-      <c r="F19" s="118"/>
-      <c r="G19" s="58"/>
-      <c r="H19" s="119"/>
-      <c r="I19" s="120"/>
-      <c r="J19" s="59"/>
-      <c r="K19" s="121"/>
-      <c r="L19" s="122"/>
-      <c r="M19" s="60"/>
-      <c r="N19" s="123"/>
-      <c r="O19" s="124"/>
-    </row>
-    <row r="20" spans="1:17" ht="30" customHeight="1">
-      <c r="A20" s="160"/>
-      <c r="B20" s="163"/>
-      <c r="C20" s="64" t="s">
+      <c r="D20" s="57"/>
+      <c r="E20" s="120"/>
+      <c r="F20" s="120"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="121"/>
+      <c r="I20" s="121"/>
+      <c r="J20" s="59"/>
+      <c r="K20" s="122"/>
+      <c r="L20" s="122"/>
+      <c r="M20" s="60"/>
+      <c r="N20" s="119"/>
+      <c r="O20" s="119"/>
+    </row>
+    <row r="21" spans="1:17" ht="30" customHeight="1">
+      <c r="A21" s="80"/>
+      <c r="B21" s="62" t="s">
         <v>39</v>
-      </c>
-      <c r="D20" s="57"/>
-      <c r="E20" s="113"/>
-      <c r="F20" s="113"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="114"/>
-      <c r="I20" s="114"/>
-      <c r="J20" s="59"/>
-      <c r="K20" s="115"/>
-      <c r="L20" s="115"/>
-      <c r="M20" s="60"/>
-      <c r="N20" s="116"/>
-      <c r="O20" s="116"/>
-    </row>
-    <row r="21" spans="1:17" ht="30" customHeight="1">
-      <c r="A21" s="160"/>
-      <c r="B21" s="62" t="s">
-        <v>40</v>
       </c>
       <c r="C21" s="63"/>
       <c r="D21" s="57"/>
-      <c r="E21" s="117"/>
-      <c r="F21" s="118"/>
+      <c r="E21" s="106"/>
+      <c r="F21" s="107"/>
       <c r="G21" s="58"/>
-      <c r="H21" s="125"/>
-      <c r="I21" s="126"/>
+      <c r="H21" s="108"/>
+      <c r="I21" s="109"/>
       <c r="J21" s="59"/>
-      <c r="K21" s="127"/>
-      <c r="L21" s="128"/>
+      <c r="K21" s="110"/>
+      <c r="L21" s="111"/>
       <c r="M21" s="60"/>
-      <c r="N21" s="116"/>
-      <c r="O21" s="116"/>
+      <c r="N21" s="119"/>
+      <c r="O21" s="119"/>
     </row>
     <row r="22" spans="1:17" ht="30" customHeight="1">
-      <c r="A22" s="161"/>
+      <c r="A22" s="81"/>
       <c r="B22" s="62" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="57"/>
-      <c r="E22" s="117"/>
-      <c r="F22" s="118"/>
+      <c r="E22" s="106"/>
+      <c r="F22" s="107"/>
       <c r="G22" s="58"/>
-      <c r="H22" s="125"/>
-      <c r="I22" s="126"/>
+      <c r="H22" s="108"/>
+      <c r="I22" s="109"/>
       <c r="J22" s="59"/>
-      <c r="K22" s="127"/>
-      <c r="L22" s="128"/>
+      <c r="K22" s="110"/>
+      <c r="L22" s="111"/>
       <c r="M22" s="60"/>
-      <c r="N22" s="116"/>
-      <c r="O22" s="116"/>
+      <c r="N22" s="119"/>
+      <c r="O22" s="119"/>
     </row>
     <row r="23" spans="1:17" ht="30" customHeight="1">
-      <c r="A23" s="156" t="s">
+      <c r="A23" s="76" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="84" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="164" t="s">
+      <c r="C23" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="64" t="s">
+      <c r="D23" s="57"/>
+      <c r="E23" s="106"/>
+      <c r="F23" s="107"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="108"/>
+      <c r="I23" s="109"/>
+      <c r="J23" s="59"/>
+      <c r="K23" s="110"/>
+      <c r="L23" s="111"/>
+      <c r="M23" s="60"/>
+      <c r="N23" s="119"/>
+      <c r="O23" s="119"/>
+    </row>
+    <row r="24" spans="1:17" ht="30" customHeight="1">
+      <c r="A24" s="76"/>
+      <c r="B24" s="85"/>
+      <c r="C24" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="D23" s="57"/>
-      <c r="E23" s="117"/>
-      <c r="F23" s="118"/>
-      <c r="G23" s="58"/>
-      <c r="H23" s="125"/>
-      <c r="I23" s="126"/>
-      <c r="J23" s="59"/>
-      <c r="K23" s="127"/>
-      <c r="L23" s="128"/>
-      <c r="M23" s="60"/>
-      <c r="N23" s="116"/>
-      <c r="O23" s="116"/>
-    </row>
-    <row r="24" spans="1:17" ht="30" customHeight="1">
-      <c r="A24" s="156"/>
-      <c r="B24" s="165"/>
-      <c r="C24" s="64" t="s">
+      <c r="D24" s="57"/>
+      <c r="E24" s="106"/>
+      <c r="F24" s="107"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="108"/>
+      <c r="I24" s="109"/>
+      <c r="J24" s="59"/>
+      <c r="K24" s="110"/>
+      <c r="L24" s="111"/>
+      <c r="M24" s="60"/>
+      <c r="N24" s="119"/>
+      <c r="O24" s="119"/>
+    </row>
+    <row r="25" spans="1:17" ht="30" customHeight="1">
+      <c r="A25" s="76"/>
+      <c r="B25" s="86"/>
+      <c r="C25" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="D24" s="57"/>
-      <c r="E24" s="117"/>
-      <c r="F24" s="118"/>
-      <c r="G24" s="58"/>
-      <c r="H24" s="125"/>
-      <c r="I24" s="126"/>
-      <c r="J24" s="59"/>
-      <c r="K24" s="127"/>
-      <c r="L24" s="128"/>
-      <c r="M24" s="60"/>
-      <c r="N24" s="116"/>
-      <c r="O24" s="116"/>
-    </row>
-    <row r="25" spans="1:17" ht="30" customHeight="1">
-      <c r="A25" s="156"/>
-      <c r="B25" s="166"/>
-      <c r="C25" s="64" t="s">
+      <c r="D25" s="57"/>
+      <c r="E25" s="106"/>
+      <c r="F25" s="107"/>
+      <c r="G25" s="58"/>
+      <c r="H25" s="108"/>
+      <c r="I25" s="109"/>
+      <c r="J25" s="59"/>
+      <c r="K25" s="110"/>
+      <c r="L25" s="111"/>
+      <c r="M25" s="60"/>
+      <c r="N25" s="119"/>
+      <c r="O25" s="119"/>
+    </row>
+    <row r="26" spans="1:17" ht="30" customHeight="1">
+      <c r="A26" s="76" t="s">
         <v>46</v>
       </c>
-      <c r="D25" s="57"/>
-      <c r="E25" s="117"/>
-      <c r="F25" s="118"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="125"/>
-      <c r="I25" s="126"/>
-      <c r="J25" s="59"/>
-      <c r="K25" s="127"/>
-      <c r="L25" s="128"/>
-      <c r="M25" s="60"/>
-      <c r="N25" s="116"/>
-      <c r="O25" s="116"/>
-    </row>
-    <row r="26" spans="1:17" ht="30" customHeight="1">
-      <c r="A26" s="156" t="s">
+      <c r="B26" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="B26" s="129" t="s">
+      <c r="C26" s="93"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="106"/>
+      <c r="F26" s="107"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="108"/>
+      <c r="I26" s="109"/>
+      <c r="J26" s="59"/>
+      <c r="K26" s="110"/>
+      <c r="L26" s="111"/>
+      <c r="M26" s="65"/>
+      <c r="N26" s="119"/>
+      <c r="O26" s="119"/>
+    </row>
+    <row r="27" spans="1:17" ht="30" customHeight="1">
+      <c r="A27" s="76"/>
+      <c r="B27" s="92" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="130"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="117"/>
-      <c r="F26" s="118"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="125"/>
-      <c r="I26" s="126"/>
-      <c r="J26" s="59"/>
-      <c r="K26" s="127"/>
-      <c r="L26" s="128"/>
-      <c r="M26" s="65"/>
-      <c r="N26" s="116"/>
-      <c r="O26" s="116"/>
-    </row>
-    <row r="27" spans="1:17" ht="30" customHeight="1">
-      <c r="A27" s="156"/>
-      <c r="B27" s="129" t="s">
+      <c r="C27" s="93"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="106"/>
+      <c r="F27" s="107"/>
+      <c r="G27" s="58"/>
+      <c r="H27" s="108"/>
+      <c r="I27" s="109"/>
+      <c r="J27" s="59"/>
+      <c r="K27" s="110"/>
+      <c r="L27" s="111"/>
+      <c r="M27" s="66"/>
+      <c r="N27" s="112"/>
+      <c r="O27" s="113"/>
+    </row>
+    <row r="28" spans="1:17" ht="30" customHeight="1">
+      <c r="A28" s="76"/>
+      <c r="B28" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="C27" s="130"/>
-      <c r="D27" s="57"/>
-      <c r="E27" s="117"/>
-      <c r="F27" s="118"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="125"/>
-      <c r="I27" s="126"/>
-      <c r="J27" s="59"/>
-      <c r="K27" s="127"/>
-      <c r="L27" s="128"/>
-      <c r="M27" s="66"/>
-      <c r="N27" s="131"/>
-      <c r="O27" s="132"/>
-    </row>
-    <row r="28" spans="1:17" ht="30" customHeight="1">
-      <c r="A28" s="156"/>
-      <c r="B28" s="129" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" s="130"/>
+      <c r="C28" s="93"/>
       <c r="D28" s="57"/>
-      <c r="E28" s="117"/>
-      <c r="F28" s="118"/>
+      <c r="E28" s="106"/>
+      <c r="F28" s="107"/>
       <c r="G28" s="58"/>
-      <c r="H28" s="125"/>
-      <c r="I28" s="126"/>
+      <c r="H28" s="108"/>
+      <c r="I28" s="109"/>
       <c r="J28" s="59"/>
-      <c r="K28" s="127"/>
-      <c r="L28" s="128"/>
+      <c r="K28" s="110"/>
+      <c r="L28" s="111"/>
       <c r="M28" s="66"/>
-      <c r="N28" s="131"/>
-      <c r="O28" s="132"/>
+      <c r="N28" s="112"/>
+      <c r="O28" s="113"/>
     </row>
     <row r="29" spans="1:17" ht="30" customHeight="1">
       <c r="A29" s="61" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="B29" s="67" t="s">
+      <c r="C29" s="67" t="s">
+        <v>51</v>
+      </c>
+      <c r="D29" s="68" t="s">
+        <v>51</v>
+      </c>
+      <c r="E29" s="114"/>
+      <c r="F29" s="114"/>
+      <c r="G29" s="58" t="s">
+        <v>51</v>
+      </c>
+      <c r="H29" s="115"/>
+      <c r="I29" s="116"/>
+      <c r="J29" s="59" t="s">
+        <v>51</v>
+      </c>
+      <c r="K29" s="117"/>
+      <c r="L29" s="118"/>
+      <c r="M29" s="69"/>
+      <c r="N29" s="119"/>
+      <c r="O29" s="119"/>
+    </row>
+    <row r="30" spans="1:17" ht="49.05" customHeight="1">
+      <c r="A30" s="91" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="67" t="s">
-        <v>52</v>
-      </c>
-      <c r="D29" s="68" t="s">
-        <v>52</v>
-      </c>
-      <c r="E29" s="133"/>
-      <c r="F29" s="133"/>
-      <c r="G29" s="58" t="s">
-        <v>52</v>
-      </c>
-      <c r="H29" s="134"/>
-      <c r="I29" s="135"/>
-      <c r="J29" s="59" t="s">
-        <v>52</v>
-      </c>
-      <c r="K29" s="136"/>
-      <c r="L29" s="137"/>
-      <c r="M29" s="69"/>
-      <c r="N29" s="116"/>
-      <c r="O29" s="116"/>
-    </row>
-    <row r="30" spans="1:17" ht="49.05" customHeight="1">
-      <c r="A30" s="138" t="s">
-        <v>53</v>
-      </c>
-      <c r="B30" s="138"/>
-      <c r="C30" s="138"/>
+      <c r="B30" s="91"/>
+      <c r="C30" s="91"/>
       <c r="D30" s="70"/>
-      <c r="E30" s="129"/>
-      <c r="F30" s="130"/>
+      <c r="E30" s="92"/>
+      <c r="F30" s="93"/>
       <c r="G30" s="71"/>
-      <c r="H30" s="139"/>
-      <c r="I30" s="140"/>
+      <c r="H30" s="94"/>
+      <c r="I30" s="95"/>
       <c r="J30" s="59"/>
-      <c r="K30" s="141"/>
-      <c r="L30" s="142"/>
+      <c r="K30" s="96"/>
+      <c r="L30" s="97"/>
       <c r="M30" s="72">
         <f>ROUND(((M18*0.45+M19*0.35+M20*0.25)*0.5+M21*0.3+M22*0.2)*0.5+(M23*0.5+M24*0.3+M25*0.2)*IF(OR(O4="A7-A9",O4="M1-M3"),0.2,0.5)+IF(OR(O4="A7-A9",O4="M1-M3"),(M26*0.3+M27*0.5+M28*0.2)*0.3,0),2)</f>
         <v>0</v>
       </c>
-      <c r="N30" s="143"/>
-      <c r="O30" s="144"/>
+      <c r="N30" s="98"/>
+      <c r="O30" s="99"/>
     </row>
     <row r="31" spans="1:17" s="39" customFormat="1" ht="24" customHeight="1">
-      <c r="A31" s="145" t="s">
+      <c r="A31" s="100" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" s="101"/>
+      <c r="C31" s="101"/>
+      <c r="D31" s="101"/>
+      <c r="E31" s="101"/>
+      <c r="F31" s="101"/>
+      <c r="G31" s="101"/>
+      <c r="H31" s="101"/>
+      <c r="I31" s="101"/>
+      <c r="J31" s="101"/>
+      <c r="K31" s="101"/>
+      <c r="L31" s="101"/>
+      <c r="M31" s="101"/>
+      <c r="N31" s="101"/>
+      <c r="O31" s="102"/>
+      <c r="Q31" s="73"/>
+    </row>
+    <row r="32" spans="1:17" s="39" customFormat="1" ht="24" customHeight="1">
+      <c r="A32" s="103" t="s">
+        <v>1</v>
+      </c>
+      <c r="B32" s="103"/>
+      <c r="C32" s="103"/>
+      <c r="D32" s="103"/>
+      <c r="E32" s="103"/>
+      <c r="F32" s="103"/>
+      <c r="G32" s="104" t="s">
+        <v>2</v>
+      </c>
+      <c r="H32" s="104"/>
+      <c r="I32" s="104"/>
+      <c r="J32" s="104" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="104"/>
+      <c r="L32" s="104"/>
+      <c r="M32" s="105" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="105"/>
+      <c r="O32" s="105"/>
+    </row>
+    <row r="33" spans="1:17" s="39" customFormat="1" ht="22.95" customHeight="1">
+      <c r="A33" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="B31" s="146"/>
-      <c r="C31" s="146"/>
-      <c r="D31" s="146"/>
-      <c r="E31" s="146"/>
-      <c r="F31" s="146"/>
-      <c r="G31" s="146"/>
-      <c r="H31" s="146"/>
-      <c r="I31" s="146"/>
-      <c r="J31" s="146"/>
-      <c r="K31" s="146"/>
-      <c r="L31" s="146"/>
-      <c r="M31" s="146"/>
-      <c r="N31" s="146"/>
-      <c r="O31" s="147"/>
-      <c r="Q31" s="73"/>
-    </row>
-    <row r="32" spans="1:17" s="39" customFormat="1" ht="24" customHeight="1">
-      <c r="A32" s="148" t="s">
-        <v>1</v>
-      </c>
-      <c r="B32" s="148"/>
-      <c r="C32" s="148"/>
-      <c r="D32" s="148"/>
-      <c r="E32" s="148"/>
-      <c r="F32" s="148"/>
-      <c r="G32" s="149" t="s">
-        <v>2</v>
-      </c>
-      <c r="H32" s="149"/>
-      <c r="I32" s="149"/>
-      <c r="J32" s="149" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="149"/>
-      <c r="L32" s="149"/>
-      <c r="M32" s="150" t="s">
-        <v>4</v>
-      </c>
-      <c r="N32" s="150"/>
-      <c r="O32" s="150"/>
-    </row>
-    <row r="33" spans="1:17" s="39" customFormat="1" ht="22.95" customHeight="1">
-      <c r="A33" s="151" t="s">
+      <c r="B33" s="87"/>
+      <c r="C33" s="87"/>
+      <c r="D33" s="87"/>
+      <c r="E33" s="87"/>
+      <c r="F33" s="87"/>
+      <c r="G33" s="88"/>
+      <c r="H33" s="88"/>
+      <c r="I33" s="88"/>
+      <c r="J33" s="89"/>
+      <c r="K33" s="89"/>
+      <c r="L33" s="89"/>
+      <c r="M33" s="90"/>
+      <c r="N33" s="90"/>
+      <c r="O33" s="90"/>
+    </row>
+    <row r="34" spans="1:17" s="39" customFormat="1" ht="22.95" customHeight="1">
+      <c r="A34" s="87" t="s">
         <v>55</v>
       </c>
-      <c r="B33" s="151"/>
-      <c r="C33" s="151"/>
-      <c r="D33" s="151"/>
-      <c r="E33" s="151"/>
-      <c r="F33" s="151"/>
-      <c r="G33" s="152"/>
-      <c r="H33" s="152"/>
-      <c r="I33" s="152"/>
-      <c r="J33" s="153"/>
-      <c r="K33" s="153"/>
-      <c r="L33" s="153"/>
-      <c r="M33" s="154"/>
-      <c r="N33" s="154"/>
-      <c r="O33" s="154"/>
-    </row>
-    <row r="34" spans="1:17" s="39" customFormat="1" ht="22.95" customHeight="1">
-      <c r="A34" s="151" t="s">
+      <c r="B34" s="87"/>
+      <c r="C34" s="87"/>
+      <c r="D34" s="87"/>
+      <c r="E34" s="87"/>
+      <c r="F34" s="87"/>
+      <c r="G34" s="88"/>
+      <c r="H34" s="88"/>
+      <c r="I34" s="88"/>
+      <c r="J34" s="89"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="89"/>
+      <c r="M34" s="90"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="90"/>
+    </row>
+    <row r="35" spans="1:17" s="39" customFormat="1" ht="22.95" customHeight="1">
+      <c r="A35" s="87" t="s">
         <v>56</v>
       </c>
-      <c r="B34" s="151"/>
-      <c r="C34" s="151"/>
-      <c r="D34" s="151"/>
-      <c r="E34" s="151"/>
-      <c r="F34" s="151"/>
-      <c r="G34" s="152"/>
-      <c r="H34" s="152"/>
-      <c r="I34" s="152"/>
-      <c r="J34" s="153"/>
-      <c r="K34" s="153"/>
-      <c r="L34" s="153"/>
-      <c r="M34" s="154"/>
-      <c r="N34" s="154"/>
-      <c r="O34" s="154"/>
-    </row>
-    <row r="35" spans="1:17" s="39" customFormat="1" ht="22.95" customHeight="1">
-      <c r="A35" s="151" t="s">
+      <c r="B35" s="87"/>
+      <c r="C35" s="87"/>
+      <c r="D35" s="87"/>
+      <c r="E35" s="87"/>
+      <c r="F35" s="87"/>
+      <c r="G35" s="88"/>
+      <c r="H35" s="88"/>
+      <c r="I35" s="88"/>
+      <c r="J35" s="89"/>
+      <c r="K35" s="89"/>
+      <c r="L35" s="89"/>
+      <c r="M35" s="90"/>
+      <c r="N35" s="90"/>
+      <c r="O35" s="90"/>
+    </row>
+    <row r="36" spans="1:17" s="39" customFormat="1" ht="22.95" customHeight="1">
+      <c r="A36" s="87" t="s">
         <v>57</v>
       </c>
-      <c r="B35" s="151"/>
-      <c r="C35" s="151"/>
-      <c r="D35" s="151"/>
-      <c r="E35" s="151"/>
-      <c r="F35" s="151"/>
-      <c r="G35" s="152"/>
-      <c r="H35" s="152"/>
-      <c r="I35" s="152"/>
-      <c r="J35" s="153"/>
-      <c r="K35" s="153"/>
-      <c r="L35" s="153"/>
-      <c r="M35" s="154"/>
-      <c r="N35" s="154"/>
-      <c r="O35" s="154"/>
-    </row>
-    <row r="36" spans="1:17" s="39" customFormat="1" ht="22.95" customHeight="1">
-      <c r="A36" s="151" t="s">
-        <v>58</v>
-      </c>
-      <c r="B36" s="151"/>
-      <c r="C36" s="151"/>
-      <c r="D36" s="151"/>
-      <c r="E36" s="151"/>
-      <c r="F36" s="151"/>
-      <c r="G36" s="152"/>
-      <c r="H36" s="152"/>
-      <c r="I36" s="152"/>
-      <c r="J36" s="153"/>
-      <c r="K36" s="153"/>
-      <c r="L36" s="153"/>
-      <c r="M36" s="154"/>
-      <c r="N36" s="154"/>
-      <c r="O36" s="154"/>
+      <c r="B36" s="87"/>
+      <c r="C36" s="87"/>
+      <c r="D36" s="87"/>
+      <c r="E36" s="87"/>
+      <c r="F36" s="87"/>
+      <c r="G36" s="88"/>
+      <c r="H36" s="88"/>
+      <c r="I36" s="88"/>
+      <c r="J36" s="89"/>
+      <c r="K36" s="89"/>
+      <c r="L36" s="89"/>
+      <c r="M36" s="90"/>
+      <c r="N36" s="90"/>
+      <c r="O36" s="90"/>
       <c r="Q36" s="39">
         <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="39" customFormat="1" ht="24" customHeight="1">
-      <c r="A37" s="155" t="s">
+      <c r="A37" s="75" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" s="75"/>
+      <c r="C37" s="75"/>
+      <c r="D37" s="75"/>
+      <c r="E37" s="75"/>
+      <c r="F37" s="75"/>
+      <c r="G37" s="75"/>
+      <c r="H37" s="75"/>
+      <c r="I37" s="75"/>
+      <c r="J37" s="75"/>
+      <c r="K37" s="75"/>
+      <c r="L37" s="75"/>
+      <c r="M37" s="75"/>
+      <c r="N37" s="75"/>
+      <c r="O37" s="75"/>
+    </row>
+    <row r="38" spans="1:17" s="39" customFormat="1" ht="22.95" customHeight="1">
+      <c r="A38" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="155"/>
-      <c r="C37" s="155"/>
-      <c r="D37" s="155"/>
-      <c r="E37" s="155"/>
-      <c r="F37" s="155"/>
-      <c r="G37" s="155"/>
-      <c r="H37" s="155"/>
-      <c r="I37" s="155"/>
-      <c r="J37" s="155"/>
-      <c r="K37" s="155"/>
-      <c r="L37" s="155"/>
-      <c r="M37" s="155"/>
-      <c r="N37" s="155"/>
-      <c r="O37" s="155"/>
-    </row>
-    <row r="38" spans="1:17" s="39" customFormat="1" ht="22.95" customHeight="1">
-      <c r="A38" s="156" t="s">
-        <v>60</v>
-      </c>
-      <c r="B38" s="156"/>
+      <c r="B38" s="76"/>
       <c r="C38" s="46"/>
       <c r="D38" s="46" t="s">
-        <v>61</v>
-      </c>
-      <c r="E38" s="156"/>
-      <c r="F38" s="156"/>
-      <c r="G38" s="156"/>
-      <c r="H38" s="156"/>
-      <c r="I38" s="156"/>
-      <c r="J38" s="156"/>
-      <c r="K38" s="156"/>
-      <c r="L38" s="156"/>
-      <c r="M38" s="156"/>
-      <c r="N38" s="156"/>
-      <c r="O38" s="156"/>
+        <v>60</v>
+      </c>
+      <c r="E38" s="76"/>
+      <c r="F38" s="76"/>
+      <c r="G38" s="76"/>
+      <c r="H38" s="76"/>
+      <c r="I38" s="76"/>
+      <c r="J38" s="76"/>
+      <c r="K38" s="76"/>
+      <c r="L38" s="76"/>
+      <c r="M38" s="76"/>
+      <c r="N38" s="76"/>
+      <c r="O38" s="76"/>
     </row>
     <row r="39" spans="1:17" s="39" customFormat="1" ht="22.95" customHeight="1">
-      <c r="A39" s="156"/>
-      <c r="B39" s="156"/>
+      <c r="A39" s="76"/>
+      <c r="B39" s="76"/>
       <c r="C39" s="46"/>
       <c r="D39" s="46" t="s">
+        <v>61</v>
+      </c>
+      <c r="E39" s="76"/>
+      <c r="F39" s="76"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="77"/>
+      <c r="I39" s="77"/>
+      <c r="J39" s="78" t="s">
         <v>62</v>
       </c>
-      <c r="E39" s="156"/>
-      <c r="F39" s="156"/>
-      <c r="G39" s="157"/>
-      <c r="H39" s="157"/>
-      <c r="I39" s="157"/>
-      <c r="J39" s="158" t="s">
+      <c r="K39" s="78"/>
+      <c r="L39" s="78"/>
+      <c r="M39" s="78" t="s">
         <v>63</v>
       </c>
-      <c r="K39" s="158"/>
-      <c r="L39" s="158"/>
-      <c r="M39" s="158" t="s">
-        <v>64</v>
-      </c>
-      <c r="N39" s="158"/>
-      <c r="O39" s="158"/>
+      <c r="N39" s="78"/>
+      <c r="O39" s="78"/>
     </row>
     <row r="40" spans="1:17" ht="24" customHeight="1">
       <c r="A40" s="74" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B40" s="74"/>
     </row>
     <row r="41" spans="1:17" ht="24" customHeight="1">
       <c r="A41" s="74" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B41" s="74"/>
     </row>
     <row r="42" spans="1:17" ht="24" customHeight="1">
       <c r="A42" s="74" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B42" s="74"/>
     </row>
     <row r="43" spans="1:17" ht="24" customHeight="1">
       <c r="A43" s="74" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B43" s="74"/>
     </row>
     <row r="44" spans="1:17" ht="24" customHeight="1">
       <c r="A44" s="74" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B44" s="74"/>
     </row>
     <row r="45" spans="1:17" ht="24" customHeight="1">
       <c r="A45" s="74" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B45" s="74"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="144">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="M5:O5"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="M6:O6"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="M7:O7"/>
+    <mergeCell ref="A8:O8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="A13:O13"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:O14"/>
+    <mergeCell ref="A15:O15"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="N29:O29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:L33"/>
+    <mergeCell ref="M33:O33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="M34:O34"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="A31:O31"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:L32"/>
+    <mergeCell ref="M32:O32"/>
     <mergeCell ref="A37:O37"/>
     <mergeCell ref="E38:O38"/>
     <mergeCell ref="E39:F39"/>
@@ -6927,126 +7058,6 @@
     <mergeCell ref="M36:O36"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="C33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:L33"/>
-    <mergeCell ref="M33:O33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="J34:L34"/>
-    <mergeCell ref="M34:O34"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="N30:O30"/>
-    <mergeCell ref="A31:O31"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:L32"/>
-    <mergeCell ref="M32:O32"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="N29:O29"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="N24:O24"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:O14"/>
-    <mergeCell ref="A15:O15"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:L12"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="A13:O13"/>
-    <mergeCell ref="A8:O8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="M5:O5"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="M6:O6"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="M7:O7"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="M4:O4"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <dataValidations count="17">
@@ -7110,7 +7121,7 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="F23:F25 P16:XFD23 A1:XFD3 A4:D6 G4:XFD4 F5:XFD5 G6:XFD6 A7:XFD8 G9:XFD9 P10:XFD12 A13:XFD15 A16:C20 F20 A21:C21 A23:C25 A29:F29 A30:C30 H29:I29 K29:L29 N29:XFD29 P30:XFD30 A37:XFD41 B35:XFD36 C33:XFD34 A31:XFD32 B42:XFD42 A22:C22 F22 F21 F16 F17 F18 F19 A26:D26 F26 A27:D27 F27 A28:D28 F28" listDataValidation="1"/>
+    <ignoredError sqref="F23:F25 P16:XFD23 A1:XFD3 A4:D6 G4:XFD4 G5:XFD5 G6:XFD6 A7:XFD8 G9:XFD9 P10:XFD12 A13:XFD15 A16:C20 F20 A21:C21 A23:C25 A29:F29 A30:C30 H29:I29 K29:L29 N29:XFD29 P30:XFD30 A37:XFD41 B35:XFD36 C33:XFD34 A31:XFD32 B42:XFD42 A22:C22 F22 F21 F16 F17 F18 F19 A26:D26 F26 A27:D27 F27 A28:D28 F28" listDataValidation="1"/>
   </ignoredErrors>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -7789,261 +7800,261 @@
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
   <sheetData>
     <row r="1" spans="1:16" ht="17.399999999999999" customHeight="1">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="176" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="176"/>
+      <c r="C1" s="176"/>
+      <c r="D1" s="176"/>
+      <c r="E1" s="176"/>
+      <c r="F1" s="176"/>
+      <c r="G1" s="176"/>
+      <c r="H1" s="176"/>
+      <c r="I1" s="176"/>
+      <c r="J1" s="176"/>
+      <c r="K1" s="176"/>
+      <c r="L1" s="176"/>
+      <c r="M1" s="176"/>
+      <c r="N1" s="176"/>
+      <c r="O1" s="176"/>
+      <c r="P1" s="176"/>
+    </row>
+    <row r="2" spans="1:16" ht="15" customHeight="1">
+      <c r="A2" s="178" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="167"/>
-      <c r="C1" s="167"/>
-      <c r="D1" s="167"/>
-      <c r="E1" s="167"/>
-      <c r="F1" s="167"/>
-      <c r="G1" s="167"/>
-      <c r="H1" s="167"/>
-      <c r="I1" s="167"/>
-      <c r="J1" s="167"/>
-      <c r="K1" s="167"/>
-      <c r="L1" s="167"/>
-      <c r="M1" s="167"/>
-      <c r="N1" s="167"/>
-      <c r="O1" s="167"/>
-      <c r="P1" s="167"/>
-    </row>
-    <row r="2" spans="1:16" ht="15" customHeight="1">
-      <c r="A2" s="177" t="s">
+      <c r="B2" s="178"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="179" t="s">
         <v>72</v>
       </c>
-      <c r="B2" s="177"/>
-      <c r="C2" s="177"/>
-      <c r="D2" s="178" t="s">
+      <c r="E2" s="179"/>
+      <c r="F2" s="177" t="s">
         <v>73</v>
       </c>
-      <c r="E2" s="178"/>
-      <c r="F2" s="168" t="s">
+      <c r="G2" s="177"/>
+      <c r="H2" s="177"/>
+      <c r="I2" s="177"/>
+      <c r="J2" s="177"/>
+      <c r="K2" s="180" t="s">
         <v>74</v>
       </c>
-      <c r="G2" s="168"/>
-      <c r="H2" s="168"/>
-      <c r="I2" s="168"/>
-      <c r="J2" s="168"/>
-      <c r="K2" s="179" t="s">
+      <c r="L2" s="180"/>
+      <c r="M2" s="180"/>
+      <c r="N2" s="180"/>
+      <c r="O2" s="180"/>
+      <c r="P2" s="180"/>
+    </row>
+    <row r="3" spans="1:16" ht="15" customHeight="1">
+      <c r="A3" s="178"/>
+      <c r="B3" s="178"/>
+      <c r="C3" s="178"/>
+      <c r="D3" s="179"/>
+      <c r="E3" s="179"/>
+      <c r="F3" s="177" t="s">
         <v>75</v>
       </c>
-      <c r="L2" s="179"/>
-      <c r="M2" s="179"/>
-      <c r="N2" s="179"/>
-      <c r="O2" s="179"/>
-      <c r="P2" s="179"/>
-    </row>
-    <row r="3" spans="1:16" ht="15" customHeight="1">
-      <c r="A3" s="177"/>
-      <c r="B3" s="177"/>
-      <c r="C3" s="177"/>
-      <c r="D3" s="178"/>
-      <c r="E3" s="178"/>
-      <c r="F3" s="168" t="s">
+      <c r="G3" s="177"/>
+      <c r="H3" s="177" t="s">
         <v>76</v>
       </c>
-      <c r="G3" s="168"/>
-      <c r="H3" s="168" t="s">
+      <c r="I3" s="177"/>
+      <c r="J3" s="177" t="s">
         <v>77</v>
       </c>
-      <c r="I3" s="168"/>
-      <c r="J3" s="168" t="s">
+      <c r="K3" s="180"/>
+      <c r="L3" s="180"/>
+      <c r="M3" s="180"/>
+      <c r="N3" s="180"/>
+      <c r="O3" s="180"/>
+      <c r="P3" s="180"/>
+    </row>
+    <row r="4" spans="1:16" ht="15">
+      <c r="A4" s="178"/>
+      <c r="B4" s="178"/>
+      <c r="C4" s="178"/>
+      <c r="D4" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="K3" s="179"/>
-      <c r="L3" s="179"/>
-      <c r="M3" s="179"/>
-      <c r="N3" s="179"/>
-      <c r="O3" s="179"/>
-      <c r="P3" s="179"/>
-    </row>
-    <row r="4" spans="1:16" ht="15">
-      <c r="A4" s="177"/>
-      <c r="B4" s="177"/>
-      <c r="C4" s="177"/>
-      <c r="D4" s="18" t="s">
+      <c r="E4" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="F4" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I4" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="J4" s="177"/>
+      <c r="K4" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="G4" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="H4" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="I4" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="J4" s="168"/>
-      <c r="K4" s="21" t="s">
+      <c r="L4" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="M4" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="L4" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="M4" s="21" t="s">
+      <c r="N4" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="N4" s="21" t="s">
+      <c r="O4" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="O4" s="21" t="s">
+      <c r="P4" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="P4" s="20" t="s">
-        <v>85</v>
-      </c>
     </row>
     <row r="5" spans="1:16" ht="15" customHeight="1">
-      <c r="A5" s="169" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="169"/>
+      <c r="A5" s="168" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="168"/>
       <c r="C5" s="23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="F5" s="175">
+        <v>51</v>
+      </c>
+      <c r="F5" s="171">
         <v>0.5</v>
       </c>
       <c r="G5" s="26"/>
-      <c r="H5" s="175">
+      <c r="H5" s="171">
         <v>0.5</v>
       </c>
       <c r="I5" s="26"/>
       <c r="J5" s="26"/>
-      <c r="K5" s="170" t="s">
-        <v>86</v>
-      </c>
-      <c r="L5" s="170"/>
-      <c r="M5" s="170"/>
-      <c r="N5" s="170"/>
-      <c r="O5" s="170"/>
-      <c r="P5" s="170"/>
+      <c r="K5" s="173" t="s">
+        <v>85</v>
+      </c>
+      <c r="L5" s="173"/>
+      <c r="M5" s="173"/>
+      <c r="N5" s="173"/>
+      <c r="O5" s="173"/>
+      <c r="P5" s="173"/>
     </row>
     <row r="6" spans="1:16" ht="15" customHeight="1">
-      <c r="A6" s="169" t="s">
+      <c r="A6" s="168" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="27" t="s">
-        <v>35</v>
-      </c>
       <c r="C6" s="23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="F6" s="175"/>
+        <v>51</v>
+      </c>
+      <c r="F6" s="171"/>
       <c r="G6" s="26"/>
-      <c r="H6" s="175"/>
+      <c r="H6" s="171"/>
       <c r="I6" s="26"/>
       <c r="J6" s="26"/>
-      <c r="K6" s="170" t="s">
+      <c r="K6" s="173" t="s">
+        <v>85</v>
+      </c>
+      <c r="L6" s="173"/>
+      <c r="M6" s="173"/>
+      <c r="N6" s="173"/>
+      <c r="O6" s="173"/>
+      <c r="P6" s="173"/>
+    </row>
+    <row r="7" spans="1:16" ht="15" customHeight="1">
+      <c r="A7" s="168"/>
+      <c r="B7" s="27" t="s">
         <v>86</v>
-      </c>
-      <c r="L6" s="170"/>
-      <c r="M6" s="170"/>
-      <c r="N6" s="170"/>
-      <c r="O6" s="170"/>
-      <c r="P6" s="170"/>
-    </row>
-    <row r="7" spans="1:16" ht="15" customHeight="1">
-      <c r="A7" s="169"/>
-      <c r="B7" s="27" t="s">
-        <v>87</v>
       </c>
       <c r="C7" s="23">
         <v>0.5</v>
       </c>
-      <c r="D7" s="173">
+      <c r="D7" s="169">
         <v>0.5</v>
       </c>
-      <c r="E7" s="175">
+      <c r="E7" s="171">
         <v>0.5</v>
       </c>
-      <c r="F7" s="175"/>
+      <c r="F7" s="171"/>
       <c r="G7" s="26"/>
-      <c r="H7" s="175"/>
+      <c r="H7" s="171"/>
       <c r="I7" s="26"/>
       <c r="J7" s="26"/>
-      <c r="K7" s="170" t="s">
-        <v>86</v>
-      </c>
-      <c r="L7" s="170"/>
-      <c r="M7" s="170"/>
-      <c r="N7" s="170"/>
-      <c r="O7" s="170"/>
-      <c r="P7" s="170"/>
+      <c r="K7" s="173" t="s">
+        <v>85</v>
+      </c>
+      <c r="L7" s="173"/>
+      <c r="M7" s="173"/>
+      <c r="N7" s="173"/>
+      <c r="O7" s="173"/>
+      <c r="P7" s="173"/>
     </row>
     <row r="8" spans="1:16" ht="15" customHeight="1">
-      <c r="A8" s="169"/>
+      <c r="A8" s="168"/>
       <c r="B8" s="27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C8" s="23">
         <v>0.3</v>
       </c>
-      <c r="D8" s="173"/>
-      <c r="E8" s="175"/>
-      <c r="F8" s="175"/>
+      <c r="D8" s="169"/>
+      <c r="E8" s="171"/>
+      <c r="F8" s="171"/>
       <c r="G8" s="26"/>
-      <c r="H8" s="175"/>
+      <c r="H8" s="171"/>
       <c r="I8" s="26"/>
       <c r="J8" s="26"/>
-      <c r="K8" s="170" t="s">
-        <v>86</v>
-      </c>
-      <c r="L8" s="170"/>
-      <c r="M8" s="170"/>
-      <c r="N8" s="170"/>
-      <c r="O8" s="170"/>
-      <c r="P8" s="170"/>
+      <c r="K8" s="173" t="s">
+        <v>85</v>
+      </c>
+      <c r="L8" s="173"/>
+      <c r="M8" s="173"/>
+      <c r="N8" s="173"/>
+      <c r="O8" s="173"/>
+      <c r="P8" s="173"/>
     </row>
     <row r="9" spans="1:16" ht="15" customHeight="1">
-      <c r="A9" s="169"/>
+      <c r="A9" s="168"/>
       <c r="B9" s="27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C9" s="23">
         <v>0.2</v>
       </c>
-      <c r="D9" s="173"/>
-      <c r="E9" s="175"/>
-      <c r="F9" s="175"/>
+      <c r="D9" s="169"/>
+      <c r="E9" s="171"/>
+      <c r="F9" s="171"/>
       <c r="G9" s="26"/>
-      <c r="H9" s="175"/>
+      <c r="H9" s="171"/>
       <c r="I9" s="26"/>
       <c r="J9" s="26"/>
-      <c r="K9" s="170" t="s">
-        <v>90</v>
-      </c>
-      <c r="L9" s="170"/>
-      <c r="M9" s="170"/>
-      <c r="N9" s="170"/>
-      <c r="O9" s="170"/>
-      <c r="P9" s="170"/>
+      <c r="K9" s="173" t="s">
+        <v>89</v>
+      </c>
+      <c r="L9" s="173"/>
+      <c r="M9" s="173"/>
+      <c r="N9" s="173"/>
+      <c r="O9" s="173"/>
+      <c r="P9" s="173"/>
     </row>
     <row r="10" spans="1:16" ht="15" customHeight="1">
       <c r="A10" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="27" t="s">
         <v>42</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>43</v>
       </c>
       <c r="C10" s="23">
         <v>1</v>
@@ -8054,51 +8065,51 @@
       <c r="E10" s="25">
         <v>0.2</v>
       </c>
-      <c r="F10" s="175">
+      <c r="F10" s="171">
         <v>0.2</v>
       </c>
       <c r="G10" s="26"/>
-      <c r="H10" s="175">
+      <c r="H10" s="171">
         <v>0.8</v>
       </c>
       <c r="I10" s="26"/>
       <c r="J10" s="26"/>
       <c r="K10" s="28"/>
       <c r="L10" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="M10" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="M10" s="28" t="s">
+      <c r="N10" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="N10" s="28" t="s">
+      <c r="O10" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="P10" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="O10" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="P10" s="29" t="s">
+    </row>
+    <row r="11" spans="1:16" ht="15" customHeight="1">
+      <c r="A11" s="168" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="27" t="s">
         <v>94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="15" customHeight="1">
-      <c r="A11" s="169" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="27" t="s">
-        <v>95</v>
       </c>
       <c r="C11" s="23">
         <v>0.3</v>
       </c>
-      <c r="D11" s="174" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="175">
+      <c r="D11" s="170" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="171">
         <v>0.3</v>
       </c>
-      <c r="F11" s="175"/>
+      <c r="F11" s="171"/>
       <c r="G11" s="26"/>
-      <c r="H11" s="175"/>
+      <c r="H11" s="171"/>
       <c r="I11" s="26"/>
       <c r="J11" s="26"/>
       <c r="K11" s="30"/>
@@ -8109,18 +8120,18 @@
       <c r="P11" s="32"/>
     </row>
     <row r="12" spans="1:16" ht="15">
-      <c r="A12" s="169"/>
+      <c r="A12" s="168"/>
       <c r="B12" s="27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C12" s="23">
         <v>0.5</v>
       </c>
-      <c r="D12" s="174"/>
-      <c r="E12" s="175"/>
-      <c r="F12" s="175"/>
+      <c r="D12" s="170"/>
+      <c r="E12" s="171"/>
+      <c r="F12" s="171"/>
       <c r="G12" s="26"/>
-      <c r="H12" s="175"/>
+      <c r="H12" s="171"/>
       <c r="I12" s="26"/>
       <c r="J12" s="33"/>
       <c r="K12" s="30"/>
@@ -8128,25 +8139,25 @@
       <c r="M12" s="30"/>
       <c r="N12" s="30"/>
       <c r="O12" s="28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P12" s="29" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="15">
+      <c r="A13" s="168"/>
+      <c r="B13" s="27" t="s">
         <v>97</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="15">
-      <c r="A13" s="169"/>
-      <c r="B13" s="27" t="s">
-        <v>98</v>
       </c>
       <c r="C13" s="23">
         <v>0.2</v>
       </c>
-      <c r="D13" s="174"/>
-      <c r="E13" s="175"/>
-      <c r="F13" s="175"/>
+      <c r="D13" s="170"/>
+      <c r="E13" s="171"/>
+      <c r="F13" s="171"/>
       <c r="G13" s="26"/>
-      <c r="H13" s="175"/>
+      <c r="H13" s="171"/>
       <c r="I13" s="26"/>
       <c r="J13" s="33"/>
       <c r="K13" s="30"/>
@@ -8157,73 +8168,91 @@
       <c r="P13" s="32"/>
     </row>
     <row r="14" spans="1:16" ht="16.05" customHeight="1">
-      <c r="A14" s="180" t="s">
+      <c r="A14" s="172" t="s">
+        <v>98</v>
+      </c>
+      <c r="B14" s="172"/>
+      <c r="C14" s="172"/>
+      <c r="D14" s="174" t="s">
         <v>99</v>
       </c>
-      <c r="B14" s="180"/>
-      <c r="C14" s="180"/>
-      <c r="D14" s="171" t="s">
+      <c r="E14" s="174"/>
+      <c r="F14" s="174"/>
+      <c r="G14" s="174"/>
+      <c r="H14" s="174"/>
+      <c r="I14" s="175" t="s">
         <v>100</v>
       </c>
-      <c r="E14" s="171"/>
-      <c r="F14" s="171"/>
-      <c r="G14" s="171"/>
-      <c r="H14" s="171"/>
-      <c r="I14" s="176" t="s">
+      <c r="J14" s="167"/>
+      <c r="K14" s="175" t="s">
         <v>101</v>
       </c>
-      <c r="J14" s="172"/>
-      <c r="K14" s="176" t="s">
+      <c r="L14" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="L14" s="36" t="s">
+      <c r="M14" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="M14" s="36" t="s">
+      <c r="N14" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="O14" s="36" t="s">
         <v>104</v>
       </c>
-      <c r="N14" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="O14" s="36" t="s">
+      <c r="P14" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="P14" s="37" t="s">
+    </row>
+    <row r="15" spans="1:16" ht="16.05" customHeight="1">
+      <c r="A15" s="172"/>
+      <c r="B15" s="172"/>
+      <c r="C15" s="172"/>
+      <c r="D15" s="167" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" ht="16.05" customHeight="1">
-      <c r="A15" s="180"/>
-      <c r="B15" s="180"/>
-      <c r="C15" s="180"/>
-      <c r="D15" s="172" t="s">
+      <c r="E15" s="167"/>
+      <c r="F15" s="167"/>
+      <c r="G15" s="167"/>
+      <c r="H15" s="167"/>
+      <c r="I15" s="175"/>
+      <c r="J15" s="167"/>
+      <c r="K15" s="175"/>
+      <c r="L15" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="E15" s="172"/>
-      <c r="F15" s="172"/>
-      <c r="G15" s="172"/>
-      <c r="H15" s="172"/>
-      <c r="I15" s="176"/>
-      <c r="J15" s="172"/>
-      <c r="K15" s="176"/>
-      <c r="L15" s="35" t="s">
+      <c r="M15" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="M15" s="34" t="s">
+      <c r="N15" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="N15" s="34" t="s">
+      <c r="O15" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="O15" s="34" t="s">
+      <c r="P15" s="38" t="s">
         <v>111</v>
-      </c>
-      <c r="P15" s="38" t="s">
-        <v>112</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="K5:P5"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="A2:C4"/>
+    <mergeCell ref="D2:E3"/>
+    <mergeCell ref="K2:P3"/>
+    <mergeCell ref="K6:P6"/>
+    <mergeCell ref="K7:P7"/>
+    <mergeCell ref="K8:P8"/>
+    <mergeCell ref="K9:P9"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="K14:K15"/>
     <mergeCell ref="D15:H15"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A11:A13"/>
@@ -8236,24 +8265,6 @@
     <mergeCell ref="H5:H9"/>
     <mergeCell ref="H10:H13"/>
     <mergeCell ref="A14:C15"/>
-    <mergeCell ref="K6:P6"/>
-    <mergeCell ref="K7:P7"/>
-    <mergeCell ref="K8:P8"/>
-    <mergeCell ref="K9:P9"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="K5:P5"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="A2:C4"/>
-    <mergeCell ref="D2:E3"/>
-    <mergeCell ref="K2:P3"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8269,15 +8280,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="181" t="s">
-        <v>72</v>
-      </c>
-      <c r="B1" s="181"/>
+      <c r="A1" s="185" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="185"/>
       <c r="C1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -8303,15 +8314,15 @@
       <c r="Z1" s="4"/>
     </row>
     <row r="2" spans="1:26" ht="284.25" customHeight="1">
-      <c r="A2" s="182" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="182"/>
+      <c r="A2" s="186" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="186"/>
       <c r="C2" s="6">
         <v>80</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -8337,17 +8348,17 @@
       <c r="Z2" s="4"/>
     </row>
     <row r="3" spans="1:26" ht="123.75" customHeight="1">
-      <c r="A3" s="183" t="s">
+      <c r="A3" s="184" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>34</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>35</v>
       </c>
       <c r="C3" s="8">
         <v>80</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -8373,21 +8384,21 @@
       <c r="Z3" s="4"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="183"/>
-      <c r="B4" s="184" t="s">
-        <v>87</v>
-      </c>
-      <c r="C4" s="184">
+      <c r="A4" s="184"/>
+      <c r="B4" s="181" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="181">
         <v>80</v>
       </c>
       <c r="D4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="F4" s="6" t="s">
         <v>38</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -8411,17 +8422,17 @@
       <c r="Z4" s="4"/>
     </row>
     <row r="5" spans="1:26" ht="165" customHeight="1">
-      <c r="A5" s="183"/>
-      <c r="B5" s="184"/>
-      <c r="C5" s="184"/>
+      <c r="A5" s="184"/>
+      <c r="B5" s="181"/>
+      <c r="C5" s="181"/>
       <c r="D5" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="E5" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="F5" s="10" t="s">
         <v>118</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>119</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
@@ -8445,15 +8456,15 @@
       <c r="Z5" s="4"/>
     </row>
     <row r="6" spans="1:26" ht="178.95" customHeight="1">
-      <c r="A6" s="183"/>
+      <c r="A6" s="184"/>
       <c r="B6" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C6" s="12">
         <v>70</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
@@ -8479,15 +8490,15 @@
       <c r="Z6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="405" customHeight="1">
-      <c r="A7" s="183"/>
+      <c r="A7" s="184"/>
       <c r="B7" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C7" s="12">
         <v>80</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E7" s="13"/>
       <c r="F7" s="13"/>
@@ -8513,23 +8524,23 @@
       <c r="Z7" s="4"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="183" t="s">
+      <c r="A8" s="184" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="181" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="184" t="s">
+      <c r="C8" s="182">
+        <v>60</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="185">
-        <v>60</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="F8" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
@@ -8553,17 +8564,17 @@
       <c r="Z8" s="4"/>
     </row>
     <row r="9" spans="1:26" ht="79.2">
-      <c r="A9" s="183"/>
-      <c r="B9" s="184"/>
-      <c r="C9" s="185"/>
+      <c r="A9" s="184"/>
+      <c r="B9" s="181"/>
+      <c r="C9" s="182"/>
       <c r="D9" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="F9" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>124</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
@@ -8587,15 +8598,15 @@
       <c r="Z9" s="4"/>
     </row>
     <row r="10" spans="1:26" ht="92.4">
-      <c r="A10" s="183"/>
+      <c r="A10" s="184"/>
       <c r="B10" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="15" t="s">
         <v>125</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>126</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="13"/>
@@ -8621,15 +8632,15 @@
       <c r="Z10" s="4"/>
     </row>
     <row r="11" spans="1:26" ht="79.2">
-      <c r="A11" s="183"/>
+      <c r="A11" s="184"/>
       <c r="B11" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="10" t="s">
         <v>127</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>128</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="13"/>
@@ -8655,15 +8666,15 @@
       <c r="Z11" s="4"/>
     </row>
     <row r="12" spans="1:26" ht="145.19999999999999">
-      <c r="A12" s="183"/>
+      <c r="A12" s="184"/>
       <c r="B12" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>130</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -8689,17 +8700,17 @@
       <c r="Z12" s="4"/>
     </row>
     <row r="13" spans="1:26" ht="185.25" customHeight="1">
-      <c r="A13" s="183" t="s">
-        <v>47</v>
+      <c r="A13" s="184" t="s">
+        <v>46</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C13" s="9">
         <v>80</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
@@ -8725,15 +8736,15 @@
       <c r="Z13" s="4"/>
     </row>
     <row r="14" spans="1:26" ht="211.2">
-      <c r="A14" s="183"/>
+      <c r="A14" s="184"/>
       <c r="B14" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="3"/>
@@ -8759,15 +8770,15 @@
       <c r="Z14" s="4"/>
     </row>
     <row r="15" spans="1:26" ht="211.2">
-      <c r="A15" s="183"/>
+      <c r="A15" s="184"/>
       <c r="B15" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="10" t="s">
         <v>133</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>134</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="3"/>
@@ -8793,21 +8804,21 @@
       <c r="Z15" s="4"/>
     </row>
     <row r="16" spans="1:26" ht="13.8" customHeight="1">
-      <c r="A16" s="183" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="183"/>
-      <c r="C16" s="186" t="s">
+      <c r="A16" s="184" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="184"/>
+      <c r="C16" s="183" t="s">
+        <v>134</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>135</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>136</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
@@ -8831,17 +8842,17 @@
       <c r="Z16" s="4"/>
     </row>
     <row r="17" spans="1:26" ht="66">
-      <c r="A17" s="183"/>
-      <c r="B17" s="183"/>
-      <c r="C17" s="186"/>
+      <c r="A17" s="184"/>
+      <c r="B17" s="184"/>
+      <c r="C17" s="183"/>
       <c r="D17" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="F17" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
